--- a/Sample Output/typical_pipe_joint_length_reference.xlsx
+++ b/Sample Output/typical_pipe_joint_length_reference.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Projects\joint-matching-algo\joint-matching-algo\Sample Output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\joint-matching-algo\Sample Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5B6D85-6B9D-4C70-933F-E0570AE072CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792C22CD-E49A-4A9A-8770-69E7585401E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5078" yWindow="1170" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Joint Length Ranges" sheetId="1" r:id="rId1"/>
+    <sheet name="confidence-diff_ratio chart" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Pipe Material</t>
   </si>
@@ -89,6 +90,30 @@
   </si>
   <si>
     <t>6 m (SRL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confidence </t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>tolerance</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Oid</t>
+  </si>
+  <si>
+    <t>New</t>
   </si>
 </sst>
 </file>
@@ -127,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -135,6 +160,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,18 +464,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="22.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,7 +494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -489,7 +514,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
@@ -506,7 +531,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -526,7 +551,7 @@
         <v>7.3330000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -546,7 +571,7 @@
         <v>7.3330000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -566,7 +591,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
@@ -583,7 +608,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -603,7 +628,7 @@
         <v>4.8890000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
@@ -620,7 +645,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -640,7 +665,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -660,7 +685,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
@@ -677,7 +702,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -697,7 +722,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
@@ -714,7 +739,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -737,4 +762,67 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C480115C-22E3-47FC-B626-7D3DD36ED082}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="16.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sample Output/typical_pipe_joint_length_reference.xlsx
+++ b/Sample Output/typical_pipe_joint_length_reference.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github Projects\joint-matching-algo\joint-matching-algo\Sample Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5B6D85-6B9D-4C70-933F-E0570AE072CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520A57BC-67AF-40AD-ACD7-55BBC9A64DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5078" yWindow="1170" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Joint Length Ranges" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Pipe Material</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>6 m (SRL)</t>
+  </si>
+  <si>
+    <t>&lt;80% 20%</t>
   </si>
 </sst>
 </file>
@@ -127,12 +130,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -437,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.73046875" style="1" bestFit="1" customWidth="1"/>
@@ -734,6 +740,14 @@
         <v>7.2</v>
       </c>
     </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C18" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
